--- a/dist/成果/防治对象/测量表/360481002211123_桂林村桂林桥03/沟道纵断面成果表_AFAE900121F00000ZACS003.xlsx
+++ b/dist/成果/防治对象/测量表/360481002211123_桂林村桂林桥03/沟道纵断面成果表_AFAE900121F00000ZACS003.xlsx
@@ -794,7 +794,7 @@
         <v>19.202</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>19.57228411537378</v>
+        <v>19.52666082926775</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>115.615752</v>
@@ -822,7 +822,7 @@
         <v>18.947</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>19.06979997762084</v>
+        <v>19.34899315445635</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.615819</v>
@@ -850,7 +850,7 @@
         <v>18.705</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>19.11370135315824</v>
+        <v>19.05027606808754</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.615866</v>
@@ -878,7 +878,7 @@
         <v>18.667</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>19.10556102689881</v>
+        <v>19.04680674570791</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.61592</v>
@@ -906,7 +906,7 @@
         <v>18.619</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>19.04956920845908</v>
+        <v>18.69011678271751</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.615973</v>
@@ -934,7 +934,7 @@
         <v>18.596</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>19.016700270081</v>
+        <v>18.76572658654649</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.616046</v>
@@ -962,7 +962,7 @@
         <v>18.519</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>18.65858248450539</v>
+        <v>18.52368289363723</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.616168</v>
@@ -990,7 +990,7 @@
         <v>18.359</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>18.43142462907349</v>
+        <v>18.71148825502321</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.616173</v>
@@ -1018,7 +1018,7 @@
         <v>18.268</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>18.32770581030562</v>
+        <v>18.30894225002853</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.61615</v>
@@ -1046,7 +1046,7 @@
         <v>18.214</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>18.49469712210713</v>
+        <v>18.57260737479946</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.616129</v>
@@ -1070,16 +1070,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
